--- a/data/trans_dic/P19C08-Estudios-trans_dic.xlsx
+++ b/data/trans_dic/P19C08-Estudios-trans_dic.xlsx
@@ -527,7 +527,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población cuyo motivo por su última visita al dentista fue por selladores, aplicación de fluor</t>
+          <t>Población cuyo motivo por su última visita al dentista fue por selladores, aplicación de fluor (tasa de respuesta: 99,78%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -717,32 +717,32 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0,14; 1,1</t>
+          <t>0,13; 1,1</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>0,26; 1,74</t>
+          <t>0,24; 1,78</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>0,2; 2,06</t>
+          <t>0,2; 1,85</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>0; 0,3</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>0,22; 1,27</t>
+          <t>0,19; 1,15</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>0,09; 1,06</t>
+          <t>0,09; 1,09</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -752,27 +752,27 @@
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>0,07; 0,61</t>
+          <t>0,07; 0,65</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>0,24; 0,94</t>
+          <t>0,22; 0,93</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>0,21; 1,06</t>
+          <t>0,26; 1,1</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>0,19; 1,09</t>
+          <t>0,19; 1,16</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>0,04; 0,36</t>
+          <t>0,04; 0,34</t>
         </is>
       </c>
     </row>
@@ -862,57 +862,57 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>0,24; 1,15</t>
+          <t>0,23; 1,16</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>0; 0,12</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>0,29; 1,16</t>
+          <t>0,29; 1,21</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>0,2; 0,98</t>
+          <t>0,19; 1,01</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0,48; 1,38</t>
+          <t>0,45; 1,34</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 0,33</t>
+          <t>0,0; 0,28</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>0,15; 0,53</t>
+          <t>0,15; 0,56</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>0,13; 0,58</t>
+          <t>0,14; 0,6</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>0,42; 1,03</t>
+          <t>0,43; 0,99</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 0,14</t>
+          <t>0,0; 0,16</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>0,26; 0,76</t>
+          <t>0,26; 0,77</t>
         </is>
       </c>
     </row>
@@ -997,12 +997,12 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0,39; 2,03</t>
+          <t>0,39; 2,23</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0,21; 1,97</t>
+          <t>0,21; 2,02</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
@@ -1012,47 +1012,47 @@
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>0,08; 0,95</t>
+          <t>0,08; 0,97</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>0,24; 2,05</t>
+          <t>0,24; 2,02</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,58</t>
+          <t>0,0; 1,57</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,73</t>
+          <t>0,0; 1,71</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>0,29; 1,8</t>
+          <t>0,33; 2,07</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>0,4; 1,63</t>
+          <t>0,42; 1,77</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>0,22; 1,24</t>
+          <t>0,22; 1,29</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>0,1; 0,99</t>
+          <t>0,1; 1,07</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>0,28; 1,18</t>
+          <t>0,25; 1,18</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>0,15; 0,64</t>
+          <t>0,15; 0,61</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>0,36; 1,01</t>
+          <t>0,36; 1,06</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>0,04; 0,39</t>
+          <t>0,04; 0,38</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>0,23; 0,82</t>
+          <t>0,25; 0,91</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>0,28; 0,89</t>
+          <t>0,29; 0,9</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>0,38; 0,92</t>
+          <t>0,39; 0,97</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>0,08; 0,48</t>
+          <t>0,08; 0,52</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>0,23; 0,6</t>
+          <t>0,23; 0,61</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>0,29; 0,66</t>
+          <t>0,29; 0,68</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>0,43; 0,89</t>
+          <t>0,43; 0,85</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>0,1; 0,35</t>
+          <t>0,08; 0,33</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>0,27; 0,61</t>
+          <t>0,29; 0,64</t>
         </is>
       </c>
     </row>
@@ -1246,7 +1246,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población cuyo motivo por su última visita al dentista fue por selladores, aplicación de fluor</t>
+          <t>Población cuyo motivo por su última visita al dentista fue por selladores, aplicación de fluor (tasa de respuesta: 99,78%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -1504,62 +1504,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>935; 7616</t>
+          <t>930; 7601</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>2009; 13526</t>
+          <t>1834; 13866</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>914; 9426</t>
+          <t>916; 8469</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>0; 1433</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>2076; 12170</t>
+          <t>1836; 11012</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>981; 11936</t>
+          <t>979; 12244</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>0; 8252</t>
+          <t>0; 8225</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>532; 4424</t>
+          <t>516; 4669</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>3945; 15479</t>
+          <t>3590; 15387</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>3964; 20124</t>
+          <t>4859; 21027</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>2062; 11933</t>
+          <t>2064; 12713</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>532; 4374</t>
+          <t>532; 4160</t>
         </is>
       </c>
     </row>
@@ -1712,62 +1712,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0; 4863</t>
+          <t>0; 4811</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>3971; 19360</t>
+          <t>3849; 19558</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0; 2036</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>6357; 25813</t>
+          <t>6455; 27029</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>2792; 13478</t>
+          <t>2653; 13817</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>7678; 22003</t>
+          <t>7080; 21289</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>0; 5602</t>
+          <t>0; 4857</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>3220; 11757</t>
+          <t>3305; 12415</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>3478; 15600</t>
+          <t>3680; 16042</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>13849; 33887</t>
+          <t>14013; 32570</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>0; 4859</t>
+          <t>0; 5472</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>11579; 33440</t>
+          <t>11696; 34213</t>
         </is>
       </c>
     </row>
@@ -1920,62 +1920,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>1764; 9153</t>
+          <t>1770; 10058</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>923; 8705</t>
+          <t>924; 8950</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>0; 5241</t>
+          <t>0; 5218</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>481; 6010</t>
+          <t>486; 6149</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>975; 8367</t>
+          <t>976; 8262</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>0; 6689</t>
+          <t>0; 6648</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>0; 8815</t>
+          <t>0; 8687</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>1889; 11705</t>
+          <t>2120; 13469</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>3477; 13982</t>
+          <t>3627; 15198</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>1898; 10694</t>
+          <t>1929; 11180</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>1041; 9998</t>
+          <t>1034; 10777</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>3573; 15083</t>
+          <t>3166; 15199</t>
         </is>
       </c>
     </row>
@@ -2128,62 +2128,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>3726; 15823</t>
+          <t>3733; 14941</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>10517; 29275</t>
+          <t>10467; 30862</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>1032; 10341</t>
+          <t>1037; 10104</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>7696; 27548</t>
+          <t>8269; 30444</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>7794; 24415</t>
+          <t>7936; 24589</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>11863; 28812</t>
+          <t>12152; 30364</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>2258; 13574</t>
+          <t>2210; 14744</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>8370; 21546</t>
+          <t>8288; 21739</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>14889; 34083</t>
+          <t>15066; 35260</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>26214; 53844</t>
+          <t>25801; 51518</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>5325; 19489</t>
+          <t>4469; 18139</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>18575; 42469</t>
+          <t>19739; 44058</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/P19C08-Estudios-trans_dic.xlsx
+++ b/data/trans_dic/P19C08-Estudios-trans_dic.xlsx
@@ -684,7 +684,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>0,24%</t>
+          <t>0,32%</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -704,7 +704,7 @@
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>0,15%</t>
+          <t>0,19%</t>
         </is>
       </c>
     </row>
@@ -717,17 +717,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0,13; 1,1</t>
+          <t>0,13; 1,15</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>0,24; 1,78</t>
+          <t>0,26; 1,93</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>0,2; 1,85</t>
+          <t>0,2; 2,07</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -737,12 +737,12 @@
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>0,19; 1,15</t>
+          <t>0,21; 1,27</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>0,09; 1,09</t>
+          <t>0,09; 1,13</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -752,27 +752,27 @@
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>0,07; 0,65</t>
+          <t>0,08; 0,72</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>0,22; 0,93</t>
+          <t>0,24; 0,96</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>0,26; 1,1</t>
+          <t>0,21; 1,05</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>0,19; 1,16</t>
+          <t>0,19; 1,08</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>0,04; 0,34</t>
+          <t>0,05; 0,48</t>
         </is>
       </c>
     </row>
@@ -804,7 +804,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>0,58%</t>
+          <t>0,74%</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -824,7 +824,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>0,3%</t>
+          <t>0,37%</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -844,7 +844,7 @@
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>0,44%</t>
+          <t>0,55%</t>
         </is>
       </c>
     </row>
@@ -862,7 +862,7 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>0,23; 1,16</t>
+          <t>0,28; 1,15</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
@@ -872,47 +872,47 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>0,29; 1,21</t>
+          <t>0,39; 1,43</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>0,19; 1,01</t>
+          <t>0,19; 0,98</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0,45; 1,34</t>
+          <t>0,44; 1,33</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 0,28</t>
+          <t>0,0; 0,33</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>0,15; 0,56</t>
+          <t>0,2; 0,7</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>0,14; 0,6</t>
+          <t>0,11; 0,56</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>0,43; 0,99</t>
+          <t>0,44; 1,07</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 0,16</t>
+          <t>0,0; 0,14</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>0,26; 0,77</t>
+          <t>0,35; 0,88</t>
         </is>
       </c>
     </row>
@@ -964,7 +964,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>0,8%</t>
+          <t>0,81%</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -997,47 +997,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0,39; 2,23</t>
+          <t>0,4; 2,27</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0,21; 2,02</t>
+          <t>0,21; 1,72</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,05</t>
+          <t>0,0; 1,04</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>0,08; 0,97</t>
+          <t>0,07; 0,97</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>0,24; 2,02</t>
+          <t>0,24; 2,27</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,57</t>
+          <t>0,0; 1,58</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,71</t>
+          <t>0,0; 1,84</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>0,33; 2,07</t>
+          <t>0,34; 1,83</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>0,42; 1,77</t>
+          <t>0,43; 1,66</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
@@ -1047,12 +1047,12 @@
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>0,1; 1,07</t>
+          <t>0,1; 1,03</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>0,25; 1,18</t>
+          <t>0,28; 1,12</t>
         </is>
       </c>
     </row>
@@ -1084,34 +1084,34 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
+          <t>0,53%</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>0,54%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>0,6%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>0,21%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
+          <t>0,44%</t>
+        </is>
+      </c>
+      <c r="K10" s="2" t="inlineStr">
+        <is>
           <t>0,45%</t>
         </is>
       </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>0,54%</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>0,6%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>0,21%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>0,38%</t>
-        </is>
-      </c>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t>0,45%</t>
-        </is>
-      </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
           <t>0,61%</t>
@@ -1124,7 +1124,7 @@
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>0,41%</t>
+          <t>0,49%</t>
         </is>
       </c>
     </row>
@@ -1137,42 +1137,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>0,15; 0,61</t>
+          <t>0,19; 0,68</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>0,36; 1,06</t>
+          <t>0,36; 1,02</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>0,04; 0,38</t>
+          <t>0,04; 0,41</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>0,25; 0,91</t>
+          <t>0,3; 0,91</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>0,29; 0,9</t>
+          <t>0,33; 0,87</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>0,39; 0,97</t>
+          <t>0,37; 0,95</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>0,08; 0,52</t>
+          <t>0,08; 0,48</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>0,23; 0,61</t>
+          <t>0,27; 0,67</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
@@ -1182,17 +1182,17 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>0,43; 0,85</t>
+          <t>0,42; 0,85</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>0,08; 0,33</t>
+          <t>0,08; 0,34</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>0,29; 0,64</t>
+          <t>0,34; 0,7</t>
         </is>
       </c>
     </row>
@@ -1471,7 +1471,7 @@
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>1764</t>
+          <t>2480</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
@@ -1491,7 +1491,7 @@
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>1764</t>
+          <t>2480</t>
         </is>
       </c>
     </row>
@@ -1504,17 +1504,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>930; 7601</t>
+          <t>928; 7908</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>1834; 13866</t>
+          <t>2029; 15040</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>916; 8469</t>
+          <t>905; 9471</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
@@ -1524,42 +1524,42 @@
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>1836; 11012</t>
+          <t>1981; 12167</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>979; 12244</t>
+          <t>979; 12736</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>0; 8225</t>
+          <t>0; 8213</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>516; 4669</t>
+          <t>651; 5685</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>3590; 15387</t>
+          <t>3948; 15808</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>4859; 21027</t>
+          <t>4070; 19922</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>2064; 12713</t>
+          <t>2051; 11877</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>532; 4160</t>
+          <t>614; 6374</t>
         </is>
       </c>
     </row>
@@ -1659,7 +1659,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>13038</t>
+          <t>15812</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1679,7 +1679,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>6558</t>
+          <t>7742</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -1699,7 +1699,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>19596</t>
+          <t>23554</t>
         </is>
       </c>
     </row>
@@ -1712,12 +1712,12 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0; 4811</t>
+          <t>0; 4862</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>3849; 19558</t>
+          <t>4655; 19439</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
@@ -1727,47 +1727,47 @@
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>6455; 27029</t>
+          <t>8380; 30665</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>2653; 13817</t>
+          <t>2588; 13484</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>7080; 21289</t>
+          <t>6923; 21067</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
+          <t>0; 5605</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
+          <t>4160; 14744</t>
+        </is>
+      </c>
+      <c r="K9" s="2" t="inlineStr">
+        <is>
+          <t>2925; 14925</t>
+        </is>
+      </c>
+      <c r="L9" s="2" t="inlineStr">
+        <is>
+          <t>14369; 35173</t>
+        </is>
+      </c>
+      <c r="M9" s="2" t="inlineStr">
+        <is>
           <t>0; 4857</t>
         </is>
       </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>3305; 12415</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>3680; 16042</t>
-        </is>
-      </c>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t>14013; 32570</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>0; 5472</t>
-        </is>
-      </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>11696; 34213</t>
+          <t>14892; 37325</t>
         </is>
       </c>
     </row>
@@ -1867,7 +1867,7 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>1947</t>
+          <t>2179</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1887,7 +1887,7 @@
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>5207</t>
+          <t>5854</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
@@ -1907,7 +1907,7 @@
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>7154</t>
+          <t>8033</t>
         </is>
       </c>
     </row>
@@ -1920,62 +1920,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>1770; 10058</t>
+          <t>1790; 10239</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>924; 8950</t>
+          <t>916; 7614</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>0; 5218</t>
+          <t>0; 5202</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>486; 6149</t>
+          <t>496; 6796</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>976; 8262</t>
+          <t>988; 9299</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>0; 6648</t>
+          <t>0; 6685</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>0; 8687</t>
+          <t>0; 9330</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>2120; 13469</t>
+          <t>2463; 13286</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>3627; 15198</t>
+          <t>3722; 14247</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>1929; 11180</t>
+          <t>1920; 11206</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>1034; 10777</t>
+          <t>1033; 10347</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>3166; 15199</t>
+          <t>3964; 15927</t>
         </is>
       </c>
     </row>
@@ -2075,7 +2075,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>14985</t>
+          <t>17992</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -2095,7 +2095,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>13529</t>
+          <t>16076</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -2115,7 +2115,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>28514</t>
+          <t>34067</t>
         </is>
       </c>
     </row>
@@ -2128,62 +2128,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>3733; 14941</t>
+          <t>4592; 16673</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>10467; 30862</t>
+          <t>10439; 29590</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>1037; 10104</t>
+          <t>1061; 10973</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>8269; 30444</t>
+          <t>10258; 30648</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>7936; 24589</t>
+          <t>8932; 23902</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>12152; 30364</t>
+          <t>11660; 29683</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>2210; 14744</t>
+          <t>2205; 13691</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>8288; 21739</t>
+          <t>9836; 24288</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>15066; 35260</t>
+          <t>15000; 35213</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>25801; 51518</t>
+          <t>25272; 51556</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>4469; 18139</t>
+          <t>4681; 18590</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>19739; 44058</t>
+          <t>23852; 49230</t>
         </is>
       </c>
     </row>
